--- a/workpaper_templates/WP06_Section100A_Risk_Assessment.xlsx
+++ b/workpaper_templates/WP06_Section100A_Risk_Assessment.xlsx
@@ -61,7 +61,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +96,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFC0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -169,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -190,6 +195,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -197,7 +217,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -564,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -688,126 +707,129 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="9" t="inlineStr"/>
       <c r="B6" s="9" t="inlineStr"/>
-      <c r="C6" s="9" t="inlineStr"/>
+      <c r="C6" s="10" t="inlineStr"/>
       <c r="D6" s="9" t="inlineStr"/>
       <c r="E6" s="9" t="inlineStr"/>
       <c r="F6" s="9" t="inlineStr"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="9" t="inlineStr"/>
       <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="9" t="inlineStr"/>
+      <c r="C7" s="10" t="inlineStr"/>
       <c r="D7" s="9" t="inlineStr"/>
       <c r="E7" s="9" t="inlineStr"/>
       <c r="F7" s="9" t="inlineStr"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="8" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="9" t="inlineStr"/>
       <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="9" t="inlineStr"/>
+      <c r="C8" s="10" t="inlineStr"/>
       <c r="D8" s="9" t="inlineStr"/>
       <c r="E8" s="9" t="inlineStr"/>
       <c r="F8" s="9" t="inlineStr"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="9" t="inlineStr"/>
       <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="9" t="inlineStr"/>
+      <c r="C9" s="10" t="inlineStr"/>
       <c r="D9" s="9" t="inlineStr"/>
       <c r="E9" s="9" t="inlineStr"/>
       <c r="F9" s="9" t="inlineStr"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="8" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="9" t="inlineStr"/>
       <c r="B10" s="9" t="inlineStr"/>
-      <c r="C10" s="9" t="inlineStr"/>
+      <c r="C10" s="10" t="inlineStr"/>
       <c r="D10" s="9" t="inlineStr"/>
       <c r="E10" s="9" t="inlineStr"/>
       <c r="F10" s="9" t="inlineStr"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="9" t="inlineStr"/>
       <c r="B11" s="9" t="inlineStr"/>
-      <c r="C11" s="9" t="inlineStr"/>
+      <c r="C11" s="10" t="inlineStr"/>
       <c r="D11" s="9" t="inlineStr"/>
       <c r="E11" s="9" t="inlineStr"/>
       <c r="F11" s="9" t="inlineStr"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="8" t="n"/>
-    </row>
-    <row r="12" ht="6" customHeight="1">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr"/>
+      <c r="C12" s="12">
+        <f>SUM(C6:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="11" t="inlineStr"/>
+      <c r="E12" s="11" t="inlineStr"/>
+      <c r="F12" s="11" t="inlineStr"/>
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13" ht="6" customHeight="1">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>B.  RISK FACTORS CHECKLIST</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Risk Factor</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Present? (Y/N)</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Reimbursement agreement in place</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
@@ -817,89 +839,93 @@
       <c r="J15" s="8" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Benefit not received by beneficiary</t>
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Reimbursement agreement in place</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr"/>
       <c r="C16" s="9" t="inlineStr"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Arrangement entered for tax benefit</t>
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Benefit not received by beneficiary</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr"/>
       <c r="C17" s="9" t="inlineStr"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Beneficiary is a low-rate taxpayer</t>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Arrangement entered for tax benefit</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr"/>
       <c r="C18" s="9" t="inlineStr"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Distribution to corporate beneficiary</t>
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Beneficiary is a low-rate taxpayer</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr"/>
       <c r="C19" s="9" t="inlineStr"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>UPE not converted to sub-trust</t>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Distribution to corporate beneficiary</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr"/>
       <c r="C20" s="9" t="inlineStr"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
-    </row>
-    <row r="21" ht="6" customHeight="1">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>UPE not converted to sub-trust</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr"/>
+      <c r="C21" s="9" t="inlineStr"/>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
@@ -908,46 +934,46 @@
       <c r="I21" s="5" t="n"/>
       <c r="J21" s="5" t="n"/>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="22" ht="6" customHeight="1">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>C.  OVERALL RISK RATING</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Risk Level</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Recommended Action</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Partner Sign-off</t>
         </is>
       </c>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="9" t="inlineStr"/>
-      <c r="B24" s="9" t="inlineStr"/>
-      <c r="C24" s="9" t="inlineStr"/>
-      <c r="D24" s="9" t="inlineStr"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
@@ -960,18 +986,18 @@
       <c r="B25" s="9" t="inlineStr"/>
       <c r="C25" s="9" t="inlineStr"/>
       <c r="D25" s="9" t="inlineStr"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
-    </row>
-    <row r="26" ht="6" customHeight="1">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="9" t="inlineStr"/>
+      <c r="B26" s="9" t="inlineStr"/>
+      <c r="C26" s="9" t="inlineStr"/>
+      <c r="D26" s="9" t="inlineStr"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
@@ -979,192 +1005,204 @@
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="27" ht="6" customHeight="1">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>D.  NOTES &amp; CONCLUSIONS</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="9" t="inlineStr"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
-      <c r="J28" s="11" t="n"/>
-    </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="9" t="inlineStr"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n"/>
-      <c r="I29" s="10" t="n"/>
-      <c r="J29" s="11" t="n"/>
+      <c r="A29" s="14" t="inlineStr"/>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="16" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="9" t="inlineStr"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n"/>
-      <c r="I30" s="10" t="n"/>
-      <c r="J30" s="11" t="n"/>
+      <c r="A30" s="14" t="inlineStr"/>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="16" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="9" t="inlineStr"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="10" t="n"/>
-      <c r="H31" s="10" t="n"/>
-      <c r="I31" s="10" t="n"/>
-      <c r="J31" s="11" t="n"/>
+      <c r="A31" s="14" t="inlineStr"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
+      <c r="H31" s="15" t="n"/>
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="16" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="9" t="inlineStr"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="n"/>
-      <c r="J32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="6" customHeight="1">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="16" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="14" t="inlineStr"/>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
+      <c r="J33" s="16" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>SIGN-OFF</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>{{preparer}}</t>
         </is>
       </c>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="15" t="n"/>
-      <c r="F35" s="13" t="inlineStr">
+      <c r="D36" s="20" t="n"/>
+      <c r="E36" s="20" t="n"/>
+      <c r="F36" s="18" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G36" s="19" t="inlineStr">
         <is>
           <t>{{date_prepared}}</t>
         </is>
       </c>
-      <c r="H35" s="15" t="n"/>
-      <c r="I35" s="15" t="n"/>
-      <c r="J35" s="15" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="H36" s="20" t="n"/>
+      <c r="I36" s="20" t="n"/>
+      <c r="J36" s="20" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>Reviewed by:</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>{{reviewer}}</t>
         </is>
       </c>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="15" t="n"/>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="20" t="n"/>
+      <c r="F37" s="18" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="G36" s="14" t="inlineStr">
+      <c r="G37" s="19" t="inlineStr">
         <is>
           <t>{{date_reviewed}}</t>
         </is>
       </c>
-      <c r="H36" s="15" t="n"/>
-      <c r="I36" s="15" t="n"/>
-      <c r="J36" s="15" t="n"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="H37" s="20" t="n"/>
+      <c r="I37" s="20" t="n"/>
+      <c r="J37" s="20" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>Notes:</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr"/>
-      <c r="C37" s="15" t="n"/>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="15" t="n"/>
-      <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
-      <c r="H37" s="15" t="n"/>
-      <c r="I37" s="15" t="n"/>
-      <c r="J37" s="15" t="n"/>
+      <c r="B38" s="20" t="inlineStr"/>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="20" t="n"/>
+      <c r="F38" s="20" t="n"/>
+      <c r="G38" s="20" t="n"/>
+      <c r="H38" s="20" t="n"/>
+      <c r="I38" s="20" t="n"/>
+      <c r="J38" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="A23:J23"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A14:J14"/>
     <mergeCell ref="A31:J31"/>
-    <mergeCell ref="B37:J37"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C37:E37"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A27:J27"/>
     <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A34:J34"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A35:J35"/>
     <mergeCell ref="G36:J36"/>
-    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="B38:J38"/>
+    <mergeCell ref="A33:J33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
